--- a/data/trans_bre/P16A15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,62</t>
+          <t>-0,42; 0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,82</t>
+          <t>-2,08; 0,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,16</t>
+          <t>-1,05; 0,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,63</t>
+          <t>-0,42; 1,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,98; 148,1</t>
+          <t>-85,59; 149,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,12</t>
+          <t>-2,12; 1,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,09</t>
+          <t>-2,6; 1,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,71</t>
+          <t>-3,85; -0,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,81</t>
+          <t>-4,32; -0,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,79; 78,02</t>
+          <t>-63,91; 67,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 48,05</t>
+          <t>-59,19; 51,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-90,59; -27,88</t>
+          <t>-91,57; -30,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,48; -24,9</t>
+          <t>-88,76; -30,58</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,99</t>
+          <t>-3,57; 1,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,35</t>
+          <t>-2,42; 4,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,26</t>
+          <t>-3,05; 3,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,52</t>
+          <t>-4,68; 3,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 51,49</t>
+          <t>-50,22; 45,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 68,52</t>
+          <t>-25,68; 71,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 55,54</t>
+          <t>-31,71; 53,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 98,16</t>
+          <t>-48,18; 88,55</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 6,25</t>
+          <t>-3,79; 6,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,06</t>
+          <t>-2,3; 8,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 9,92</t>
+          <t>-0,51; 10,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,18</t>
+          <t>-3,93; 4,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 54,82</t>
+          <t>-23,76; 54,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 53,45</t>
+          <t>-10,86; 52,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 75,51</t>
+          <t>-2,77; 81,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 23,86</t>
+          <t>-17,37; 25,04</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 13,27</t>
+          <t>0,62; 13,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 6,47</t>
+          <t>-10,35; 4,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 5,4</t>
+          <t>-8,04; 5,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 53,7</t>
+          <t>2,47; 51,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 89,41</t>
+          <t>1,66; 89,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 21,02</t>
+          <t>-25,76; 16,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 20,4</t>
+          <t>-24,73; 21,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 200,22</t>
+          <t>8,33; 196,37</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 11,95</t>
+          <t>-2,21; 12,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 11,97</t>
+          <t>-3,81; 11,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 9,64</t>
+          <t>-5,28; 9,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 11,81</t>
+          <t>0,54; 12,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 77,04</t>
+          <t>-9,6; 83,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 44,26</t>
+          <t>-10,69; 43,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 37,57</t>
+          <t>-16,45; 37,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 36,57</t>
+          <t>1,39; 38,38</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,38</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,63</t>
+          <t>0,36; 3,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,14</t>
+          <t>0,16; 3,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 23,36</t>
+          <t>1,59; 22,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,64; 63,22</t>
+          <t>13,13; 61,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 37,98</t>
+          <t>3,86; 38,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 35,28</t>
+          <t>1,35; 34,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,59; 222,99</t>
+          <t>13,57; 227,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>175,98%</t>
+          <t>195,21%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,73</t>
+          <t>-0,51; 0,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,78</t>
+          <t>-2,04; 0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,21</t>
+          <t>-1,14; 0,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,61</t>
+          <t>-0,36; 1,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,59; 149,57</t>
+          <t>-87,76; 117,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-70,91%</t>
+          <t>-60,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,06</t>
+          <t>-1,96; 1,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,14</t>
+          <t>-2,89; 1,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,76</t>
+          <t>-3,82; -0,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,76</t>
+          <t>-3,83; -0,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,91; 67,07</t>
+          <t>-65,3; 86,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,19; 51,11</t>
+          <t>-60,07; 60,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-91,57; -30,92</t>
+          <t>-90,18; -35,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-88,76; -30,58</t>
+          <t>-81,21; -15,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,01%</t>
+          <t>-35,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,83</t>
+          <t>-3,59; 1,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,56</t>
+          <t>-2,23; 4,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,18</t>
+          <t>-3,29; 3,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,01</t>
+          <t>-5,8; -0,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 45,84</t>
+          <t>-51,32; 42,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 71,1</t>
+          <t>-24,19; 70,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 53,63</t>
+          <t>-34,49; 52,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 88,55</t>
+          <t>-54,55; -8,71</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,28</t>
+          <t>-3,52; 5,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,88</t>
+          <t>-2,3; 8,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 10,1</t>
+          <t>-0,81; 9,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,44</t>
+          <t>-2,53; 5,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 54,8</t>
+          <t>-22,13; 51,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 52,48</t>
+          <t>-10,54; 55,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 81,43</t>
+          <t>-5,38; 71,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 25,04</t>
+          <t>-11,88; 33,19</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,23</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 13,18</t>
+          <t>0,58; 13,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 4,95</t>
+          <t>-9,34; 5,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 5,53</t>
+          <t>-8,45; 5,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 51,67</t>
+          <t>0,61; 9,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 89,24</t>
+          <t>2,2; 90,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 16,38</t>
+          <t>-24,66; 19,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 21,02</t>
+          <t>-24,73; 20,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,33; 196,37</t>
+          <t>1,01; 40,71</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 12,34</t>
+          <t>-1,92; 11,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,7</t>
+          <t>-4,18; 11,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 9,68</t>
+          <t>-6,27; 8,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 12,04</t>
+          <t>0,33; 11,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 83,22</t>
+          <t>-9,1; 75,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 43,66</t>
+          <t>-11,67; 42,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 37,97</t>
+          <t>-19,43; 35,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 38,38</t>
+          <t>0,63; 35,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,86; 3,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,68</t>
+          <t>0,44; 3,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,1</t>
+          <t>0,1; 3,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 22,44</t>
+          <t>0,58; 3,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,13; 61,62</t>
+          <t>13,46; 62,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,86; 38,66</t>
+          <t>3,95; 36,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 34,84</t>
+          <t>0,76; 35,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,57; 227,26</t>
+          <t>4,5; 28,87</t>
         </is>
       </c>
     </row>
